--- a/Mediciones/RNA/T/RUN1_T_2NO.xlsx
+++ b/Mediciones/RNA/T/RUN1_T_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\T\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7DDFA3-61D2-4ED4-96D3-EB5DCF65933D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCEDAD1-4C47-4BBC-A5BA-821DDAC04A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -413,6 +413,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T22:08:02",
   "bounds": {
@@ -423,7 +426,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -514,9 +517,6 @@
   "run_id": "R20260718_220802",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D2">
         <v>0.67644183773216027</v>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D3">
         <v>0.67644183773216027</v>
@@ -1082,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D4">
         <v>0.67644183773216027</v>
@@ -1135,7 +1135,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5">
         <v>0.67644183773216027</v>
@@ -1188,7 +1188,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D6">
         <v>0.67644183773216027</v>
@@ -1241,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D7">
         <v>0.67644183773216027</v>
@@ -1294,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D8">
         <v>0.68230694037145645</v>
@@ -1347,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D9">
         <v>0.68230694037145645</v>
@@ -1400,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D10">
         <v>0.68230694037145645</v>
@@ -1453,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D11">
         <v>0.68230694037145645</v>
@@ -1506,7 +1506,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12">
         <v>0.68230694037145645</v>
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D13">
         <v>0.68230694037145645</v>
@@ -1612,7 +1612,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D14">
         <v>0.68230694037145645</v>
@@ -1665,7 +1665,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D15">
         <v>0.68230694037145645</v>
@@ -1718,7 +1718,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D16">
         <v>0.68230694037145645</v>
@@ -1771,7 +1771,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D17">
         <v>0.68230694037145645</v>
@@ -1824,7 +1824,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D18">
         <v>0.68230694037145645</v>
@@ -1877,7 +1877,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D19">
         <v>0.68230694037145645</v>
@@ -1930,7 +1930,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D20">
         <v>0.68230694037145645</v>
@@ -1983,7 +1983,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21">
         <v>0.68230694037145645</v>
@@ -2036,7 +2036,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D22">
         <v>0.68230694037145645</v>
@@ -2089,7 +2089,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D23">
         <v>0.68230694037145645</v>
@@ -2142,7 +2142,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D24">
         <v>0.68230694037145645</v>
@@ -2195,7 +2195,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D25">
         <v>0.68230694037145645</v>
@@ -2248,7 +2248,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D26">
         <v>0.68230694037145645</v>
@@ -2301,7 +2301,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D27">
         <v>0.68230694037145645</v>
@@ -2354,7 +2354,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D28">
         <v>0.68230694037145645</v>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D29">
         <v>0.68230694037145645</v>
@@ -2460,7 +2460,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D30">
         <v>0.68230694037145645</v>
@@ -2513,7 +2513,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D31">
         <v>0.68230694037145645</v>
@@ -2566,7 +2566,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32">
         <v>0.68230694037145645</v>
@@ -2619,7 +2619,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D33">
         <v>0.68230694037145645</v>
@@ -2672,7 +2672,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D34">
         <v>0.68230694037145645</v>
@@ -2725,7 +2725,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D35">
         <v>0.68230694037145645</v>
@@ -2778,7 +2778,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D36">
         <v>0.68230694037145645</v>
@@ -2831,7 +2831,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D37">
         <v>0.68230694037145645</v>
@@ -2884,7 +2884,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D38">
         <v>0.68230694037145645</v>
@@ -2937,7 +2937,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39">
         <v>0.68230694037145645</v>
@@ -2990,7 +2990,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D40">
         <v>0.68230694037145645</v>
@@ -3043,7 +3043,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D41">
         <v>0.68230694037145645</v>
@@ -3096,7 +3096,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D42">
         <v>0.68230694037145645</v>
@@ -3149,7 +3149,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D43">
         <v>0.68230694037145645</v>
@@ -3202,7 +3202,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D44">
         <v>0.68230694037145645</v>
@@ -3255,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D45">
         <v>0.68230694037145645</v>
@@ -3308,7 +3308,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D46">
         <v>0.68230694037145645</v>
@@ -3361,7 +3361,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D47">
         <v>0.68230694037145645</v>
@@ -3414,7 +3414,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D48">
         <v>0.68230694037145645</v>
@@ -3467,7 +3467,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D49">
         <v>0.68230694037145645</v>
@@ -3520,7 +3520,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D50">
         <v>0.68230694037145645</v>
@@ -3573,7 +3573,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D51">
         <v>0.68230694037145645</v>
@@ -3626,7 +3626,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D52">
         <v>0.71554252199413493</v>
@@ -3679,7 +3679,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D53">
         <v>0.71554252199413493</v>
@@ -3732,7 +3732,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D54">
         <v>0.71554252199413493</v>
@@ -3785,7 +3785,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D55">
         <v>0.71554252199413493</v>
@@ -3838,7 +3838,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D56">
         <v>0.72922776148582602</v>
@@ -3891,7 +3891,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D57">
         <v>0.72922776148582602</v>
@@ -3944,7 +3944,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D58">
         <v>0.72922776148582602</v>
@@ -3997,7 +3997,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D59">
         <v>0.72922776148582602</v>
@@ -4050,7 +4050,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D60">
         <v>0.72922776148582602</v>
@@ -4103,7 +4103,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D61">
         <v>0.72922776148582602</v>
@@ -4156,7 +4156,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D62">
         <v>0.72922776148582602</v>
@@ -4209,7 +4209,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D63">
         <v>0.72922776148582602</v>
@@ -4262,7 +4262,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D64">
         <v>0.72922776148582602</v>
@@ -4315,7 +4315,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D65">
         <v>0.72922776148582602</v>
@@ -4368,7 +4368,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D66">
         <v>0.72922776148582602</v>
@@ -4421,7 +4421,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D67">
         <v>0.72922776148582602</v>
@@ -4474,7 +4474,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D68">
         <v>0.72922776148582602</v>
@@ -4527,7 +4527,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D69">
         <v>0.72922776148582602</v>
@@ -4580,7 +4580,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D70">
         <v>0.72922776148582602</v>
@@ -4633,7 +4633,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D71">
         <v>0.72922776148582602</v>
@@ -4686,7 +4686,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D72">
         <v>0.72922776148582602</v>
@@ -4739,7 +4739,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D73">
         <v>0.72922776148582602</v>
@@ -4792,7 +4792,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D74">
         <v>0.72922776148582602</v>
@@ -4845,7 +4845,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D75">
         <v>0.72922776148582602</v>
@@ -4898,7 +4898,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D76">
         <v>0.72922776148582602</v>
@@ -4951,7 +4951,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D77">
         <v>0.72922776148582602</v>
@@ -5004,7 +5004,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D78">
         <v>0.72922776148582602</v>
@@ -5057,7 +5057,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D79">
         <v>0.72922776148582602</v>
@@ -5110,7 +5110,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D80">
         <v>0.72922776148582602</v>
@@ -5163,7 +5163,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D81">
         <v>0.72922776148582602</v>
@@ -5216,7 +5216,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D82">
         <v>0.72922776148582602</v>
@@ -5269,7 +5269,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D83">
         <v>0.72922776148582602</v>
@@ -5322,7 +5322,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D84">
         <v>0.72922776148582602</v>
@@ -5375,7 +5375,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D85">
         <v>0.72922776148582602</v>
@@ -5428,7 +5428,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D86">
         <v>0.72922776148582602</v>
@@ -5481,7 +5481,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D87">
         <v>0.72922776148582602</v>
@@ -5534,7 +5534,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D88">
         <v>0.72922776148582602</v>
@@ -5587,7 +5587,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D89">
         <v>0.72922776148582602</v>
@@ -5640,7 +5640,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D90">
         <v>0.72922776148582602</v>
@@ -5693,7 +5693,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D91">
         <v>0.72922776148582602</v>
@@ -5746,7 +5746,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D92">
         <v>0.72922776148582602</v>
@@ -5799,7 +5799,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D93">
         <v>0.72922776148582602</v>
@@ -5852,7 +5852,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D94">
         <v>0.72922776148582602</v>
@@ -5905,7 +5905,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D95">
         <v>0.72922776148582602</v>
@@ -5958,7 +5958,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D96">
         <v>0.72922776148582602</v>
@@ -6011,7 +6011,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D97">
         <v>0.72922776148582602</v>
@@ -6064,7 +6064,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D98">
         <v>0.72922776148582602</v>
@@ -6117,7 +6117,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D99">
         <v>0.72922776148582602</v>
@@ -6170,7 +6170,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D100">
         <v>0.72922776148582602</v>
@@ -6223,7 +6223,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D101">
         <v>0.72922776148582602</v>
@@ -6276,7 +6276,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D102">
         <v>0.72922776148582602</v>
@@ -6329,7 +6329,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D103">
         <v>0.72922776148582602</v>
@@ -6382,7 +6382,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D104">
         <v>0.72922776148582602</v>
@@ -6435,7 +6435,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D105">
         <v>0.72922776148582602</v>
@@ -6488,7 +6488,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D106">
         <v>0.72922776148582602</v>
@@ -6541,7 +6541,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D107">
         <v>0.72922776148582602</v>
@@ -6594,7 +6594,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D108">
         <v>0.72922776148582602</v>
@@ -6647,7 +6647,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D109">
         <v>0.72922776148582602</v>
@@ -6700,7 +6700,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D110">
         <v>0.72922776148582602</v>
@@ -6753,7 +6753,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D111">
         <v>0.72922776148582602</v>
@@ -6806,7 +6806,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D112">
         <v>0.72922776148582602</v>
@@ -6859,7 +6859,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D113">
         <v>0.72922776148582602</v>
@@ -6912,7 +6912,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D114">
         <v>0.72922776148582602</v>
@@ -6965,7 +6965,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D115">
         <v>0.72922776148582602</v>
@@ -7018,7 +7018,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D116">
         <v>0.72922776148582602</v>
@@ -7071,7 +7071,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D117">
         <v>0.72922776148582602</v>
@@ -7124,7 +7124,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D118">
         <v>0.72922776148582602</v>
@@ -7177,7 +7177,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D119">
         <v>0.72922776148582602</v>
@@ -7230,7 +7230,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D120">
         <v>0.72922776148582602</v>
@@ -7283,7 +7283,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D121">
         <v>0.72922776148582602</v>
@@ -14576,7 +14576,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
